--- a/SQExcel.Portal/src/content/docs/ja/docs/images/data-import-dialog/data-import-dialog.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/data-import-dialog/data-import-dialog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\data-import-dialog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\data-import-dialog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694A9823-07DF-432E-A350-4BC06518DFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C9D31D-188A-4A2D-B14B-CA32FE4016F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="590" yWindow="1370" windowWidth="21200" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3160" yWindow="2230" windowWidth="19750" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data-import-dialog" sheetId="3" r:id="rId1"/>
@@ -1560,10 +1560,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="53" name="グループ化 52">
+        <xdr:cNvPr id="30" name="グループ化 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44112C2-B3E1-D27D-4D6F-5594CB4538CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6191330D-BFDC-0AD6-08D1-DC6D7CED00D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1573,39 +1573,88 @@
         <a:xfrm>
           <a:off x="246529" y="10428942"/>
           <a:ext cx="8520057" cy="3601971"/>
-          <a:chOff x="9398000" y="11430000"/>
+          <a:chOff x="249891" y="10294471"/>
           <a:chExt cx="8641080" cy="3557148"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="52" name="図 51">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F106CB-83B5-E4C5-A37F-6DFAB330027A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="29" name="グループ化 28">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{400E71E3-753F-60D1-38B0-27034ACE3BC3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="9398000" y="11430000"/>
+            <a:off x="249891" y="10294471"/>
             <a:ext cx="8641080" cy="3557148"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
+            <a:chOff x="249891" y="10294471"/>
+            <a:chExt cx="8641080" cy="3557148"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="52" name="図 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F106CB-83B5-E4C5-A37F-6DFAB330027A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="249891" y="10294471"/>
+              <a:ext cx="8641080" cy="3557148"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="20" name="図 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B563BD5-CC41-486F-A30C-32E2F8CB5D90}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="279774" y="10339294"/>
+              <a:ext cx="252071" cy="225939"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="22" name="正方形/長方形 21">
@@ -1619,8 +1668,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9531223" y="11948845"/>
-            <a:ext cx="8408317" cy="1394492"/>
+            <a:off x="381248" y="10813878"/>
+            <a:ext cx="8411577" cy="1394135"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1674,8 +1723,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9531223" y="13436909"/>
-            <a:ext cx="8408317" cy="731746"/>
+            <a:off x="381248" y="12302764"/>
+            <a:ext cx="8411577" cy="729014"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1729,8 +1778,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="9531223" y="14165203"/>
-            <a:ext cx="8408317" cy="801591"/>
+            <a:off x="381248" y="13031270"/>
+            <a:ext cx="8411577" cy="799739"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1784,8 +1833,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="17303679" y="12033913"/>
-            <a:ext cx="471045" cy="266692"/>
+            <a:off x="8155785" y="10900018"/>
+            <a:ext cx="471172" cy="267065"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1844,8 +1893,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="17303679" y="13530816"/>
-            <a:ext cx="471046" cy="266692"/>
+            <a:off x="8155785" y="12394865"/>
+            <a:ext cx="471173" cy="267065"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1904,8 +1953,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="17303679" y="14311784"/>
-            <a:ext cx="478042" cy="266692"/>
+            <a:off x="8155785" y="13176710"/>
+            <a:ext cx="478071" cy="267064"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -1964,8 +2013,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="14447518" y="14229742"/>
-            <a:ext cx="581534" cy="266377"/>
+            <a:off x="5299285" y="13093634"/>
+            <a:ext cx="583474" cy="266745"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst/>
@@ -2073,7 +2122,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2617,50 +2666,6 @@
         </xdr:txBody>
       </xdr:sp>
     </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>7471</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>29881</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>190351</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>83856</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="図 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16F1F1C5-1061-06BB-4BE3-1188DE4A34FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="470647" y="724646"/>
-          <a:ext cx="8520057" cy="8622739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -4827,6 +4832,99 @@
           </a:fontRef>
         </xdr:style>
       </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7471</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>29881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>190351</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>83856</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="19" name="グループ化 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{418BB173-CDE5-7C87-72D9-F9368E3FBC93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="470647" y="724646"/>
+          <a:ext cx="8520057" cy="8622739"/>
+          <a:chOff x="477371" y="715681"/>
+          <a:chExt cx="8641080" cy="8512175"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="45" name="図 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16F1F1C5-1061-06BB-4BE3-1188DE4A34FE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="477371" y="715681"/>
+            <a:ext cx="8641080" cy="8512175"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="9" name="図 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E52CAE-5670-4CD1-A568-5A342F494BF3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="522194" y="775447"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
